--- a/evaluation_forms/015_language_acquisition_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/015_language_acquisition_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>School Name</t>
+          <t>School Name2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Teacher Name</t>
+          <t>Teacher Name2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Student Name2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Student Age</t>
+          <t>Student Age2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
